--- a/artfynd/A 43982-2023 artfynd.xlsx
+++ b/artfynd/A 43982-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119018346</v>
+        <v>119018368</v>
       </c>
       <c r="B2" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554192</v>
+        <v>554296</v>
       </c>
       <c r="R2" t="n">
-        <v>6953394</v>
+        <v>6953409</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119018369</v>
+        <v>119018362</v>
       </c>
       <c r="B3" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554350</v>
+        <v>554435</v>
       </c>
       <c r="R3" t="n">
-        <v>6953337</v>
+        <v>6953403</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,18 +845,12 @@
           <t>2024-07-13</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>100 bladrosetter, 4 blomställningar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119018364</v>
+        <v>119018363</v>
       </c>
       <c r="B4" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553540</v>
+        <v>554443</v>
       </c>
       <c r="R4" t="n">
-        <v>6953852</v>
+        <v>6953314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119018352</v>
+        <v>119018365</v>
       </c>
       <c r="B5" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553985</v>
+        <v>554064</v>
       </c>
       <c r="R5" t="n">
-        <v>6953481</v>
+        <v>6953511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119018368</v>
+        <v>119018366</v>
       </c>
       <c r="B6" t="n">
-        <v>78247</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,7 +1101,7 @@
         <v>554296</v>
       </c>
       <c r="R6" t="n">
-        <v>6953409</v>
+        <v>6953497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,50 +1160,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119018349</v>
+        <v>119018359</v>
       </c>
       <c r="B7" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553601</v>
+        <v>553888</v>
       </c>
       <c r="R7" t="n">
-        <v>6953340</v>
+        <v>6953404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,50 +1265,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119018353</v>
+        <v>119018360</v>
       </c>
       <c r="B8" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554044</v>
+        <v>553663</v>
       </c>
       <c r="R8" t="n">
-        <v>6953493</v>
+        <v>6953617</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,15 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119018355</v>
+        <v>119018367</v>
       </c>
       <c r="B9" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554173</v>
+        <v>554171</v>
       </c>
       <c r="R9" t="n">
-        <v>6953589</v>
+        <v>6953591</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,50 +1467,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119018363</v>
+        <v>119018369</v>
       </c>
       <c r="B10" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554443</v>
+        <v>554350</v>
       </c>
       <c r="R10" t="n">
-        <v>6953314</v>
+        <v>6953337</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,12 +1544,18 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>100 bladrosetter, 4 blomställningar</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1603,37 +1574,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119018366</v>
+        <v>119018361</v>
       </c>
       <c r="B11" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554296</v>
+        <v>554405</v>
       </c>
       <c r="R11" t="n">
-        <v>6953497</v>
+        <v>6953502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,6 +1653,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1705,15 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119018351</v>
+        <v>119018346</v>
       </c>
       <c r="B12" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553663</v>
+        <v>554192</v>
       </c>
       <c r="R12" t="n">
-        <v>6953778</v>
+        <v>6953394</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,37 +1769,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119018365</v>
+        <v>119018349</v>
       </c>
       <c r="B13" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554064</v>
+        <v>553601</v>
       </c>
       <c r="R13" t="n">
-        <v>6953511</v>
+        <v>6953340</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,15 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119018357</v>
+        <v>119018350</v>
       </c>
       <c r="B14" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,10 +1901,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554215</v>
+        <v>553657</v>
       </c>
       <c r="R14" t="n">
-        <v>6953491</v>
+        <v>6953605</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,15 +1963,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119018358</v>
+        <v>119018351</v>
       </c>
       <c r="B15" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,10 +1998,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554453</v>
+        <v>553663</v>
       </c>
       <c r="R15" t="n">
-        <v>6953506</v>
+        <v>6953778</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,15 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119018350</v>
+        <v>119018352</v>
       </c>
       <c r="B16" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553657</v>
+        <v>553985</v>
       </c>
       <c r="R16" t="n">
-        <v>6953605</v>
+        <v>6953481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,37 +2157,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119018362</v>
+        <v>119018353</v>
       </c>
       <c r="B17" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2192,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>554435</v>
+        <v>554044</v>
       </c>
       <c r="R17" t="n">
-        <v>6953403</v>
+        <v>6953493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,15 +2254,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119018367</v>
+        <v>119018354</v>
       </c>
       <c r="B18" t="n">
-        <v>97780</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,21 +2265,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2289,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554171</v>
+        <v>554094</v>
       </c>
       <c r="R18" t="n">
-        <v>6953591</v>
+        <v>6953524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,58 +2351,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119018359</v>
+        <v>119018355</v>
       </c>
       <c r="B19" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553888</v>
+        <v>554173</v>
       </c>
       <c r="R19" t="n">
-        <v>6953404</v>
+        <v>6953589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,6 +2445,297 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>119018357</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>554215</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6953491</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl, Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>119018358</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>554453</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6953506</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl, Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119018364</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>553540</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6953852</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl, Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43982-2023 artfynd.xlsx
+++ b/artfynd/A 43982-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018368</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018362</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018363</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018364</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018365</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018366</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018359</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018360</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018367</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1668,6 +1718,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018369</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018361</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018346</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018349</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2057,6 +2127,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018350</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018351</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2251,6 +2331,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018352</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018353</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2445,6 +2535,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018354</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2542,6 +2637,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018355</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2639,6 +2739,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018357</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2736,8 +2841,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018358</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>